--- a/StructureDefinition-openimis-communication-request.xlsx
+++ b/StructureDefinition-openimis-communication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1243,60 +1243,60 @@
     <t>Drug Received? (yes|no)</t>
   </si>
   <si>
-    <t>CommunicationRequest.payload:Asessment</t>
-  </si>
-  <si>
-    <t>Asessment</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.id</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.extension</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.extension:type</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.extension:type.id</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.extension:type.extension</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.extension:type.url</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.extension:type.value[x]</t>
+    <t>CommunicationRequest.payload:assessment</t>
+  </si>
+  <si>
+    <t>assessment</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.id</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.extension</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.extension:type</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.extension:type.id</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.extension:type.extension</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.extension:type.url</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.extension:type.value[x]</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="https://github.com/openimis/openimis_fhir_r5_ig/CodeSystem/feedback-payload"/&gt;
-    &lt;code value="Asessment"/&gt;
+    &lt;code value="assessment"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>CommunicationRequest.payload:Asessment.modifierExtension</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.content[x]</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.content[x].id</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.content[x].extension</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.content[x].coding</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload:Asessment.content[x].text</t>
-  </si>
-  <si>
-    <t>Asessment? (0|1|2|3|4|5)</t>
+    <t>CommunicationRequest.payload:assessment.modifierExtension</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.content[x]</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.content[x].id</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.content[x].extension</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.content[x].coding</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload:assessment.content[x].text</t>
+  </si>
+  <si>
+    <t>assessment? (0|1|2|3|4|5)</t>
   </si>
   <si>
     <t>CommunicationRequest.occurrence[x]</t>
@@ -2940,7 +2940,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>22</v>
@@ -3053,7 +3053,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>22</v>
@@ -3164,7 +3164,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>22</v>
@@ -3277,7 +3277,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>22</v>
@@ -3717,7 +3717,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>22</v>
@@ -3828,7 +3828,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>22</v>
@@ -3939,7 +3939,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>22</v>
@@ -4052,7 +4052,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>22</v>
@@ -4381,7 +4381,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>22</v>
@@ -12870,7 +12870,7 @@
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>22</v>
@@ -12979,7 +12979,7 @@
         <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>22</v>
@@ -13088,7 +13088,7 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>22</v>
@@ -13306,7 +13306,7 @@
         <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>22</v>
@@ -13415,7 +13415,7 @@
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>22</v>
@@ -13526,7 +13526,7 @@
         <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-communication-request.xlsx
+++ b/StructureDefinition-openimis-communication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-communication-request.xlsx
+++ b/StructureDefinition-openimis-communication-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
